--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T10:14:31+00:00</t>
+    <t>2026-07-08T15:46:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T15:46:54+00:00</t>
+    <t>2026-07-09T09:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:13:13+00:00</t>
+    <t>2026-07-10T12:01:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:01:50+00:00</t>
+    <t>2026-07-10T12:28:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:28:44+00:00</t>
+    <t>2026-07-10T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T12:58:40+00:00</t>
+    <t>2026-07-20T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:08:41+00:00</t>
+    <t>2026-07-21T09:08:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:08:11+00:00</t>
+    <t>2026-07-21T09:10:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:10:59+00:00</t>
+    <t>2026-07-22T09:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T09:27:19+00:00</t>
+    <t>2026-07-28T07:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T07:28:06+00:00</t>
+    <t>2026-07-30T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T08:11:50+00:00</t>
+    <t>2026-08-03T07:00:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1009,7 +1009,7 @@
     <t>serviceRequestAccessionNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-service-request-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-service-request-imaging-document|0.1.0)
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T07:00:21+00:00</t>
+    <t>2026-08-04T07:50:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:50:37+00:00</t>
+    <t>2026-08-04T08:17:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:17:33+00:00</t>
+    <t>2026-08-06T12:56:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T12:56:12+00:00</t>
+    <t>2026-08-07T08:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T08:15:28+00:00</t>
+    <t>2026-08-07T09:41:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:41:31+00:00</t>
+    <t>2026-08-07T12:53:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T12:53:43+00:00</t>
+    <t>2026-09-03T14:46:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1966,7 +1966,7 @@
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-quantite-exposition-rayonnements-cisis|20260619134041</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-quantite-exposition-rayonnements-cisis|20260716085851</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR 
--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T14:46:57+00:00</t>
+    <t>2026-09-04T09:26:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-radiation-exposure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:26:41+00:00</t>
+    <t>2026-09-04T11:53:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
